--- a/売上レポート/売上集計_2026年6-9月.xlsx
+++ b/売上レポート/売上集計_2026年6-9月.xlsx
@@ -1399,7 +1399,7 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>・7月は7/21〜7/24の日別報告なし。また7/26は訂正後の695,890円を採用。</t>
+          <t>・7月は7/21〜7/24の日別報告なし。7/26は訂正後の695,890円（7月合算13,369,100）を採用。</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="I57" s="16" t="inlineStr">
         <is>
-          <t>当初965,890で報告→7/27に695,890へ訂正（訂正文では「6月26日」と記載）</t>
+          <t>当初965,890で報告→7/27に「7月26日 695,890／7月合算 13,369,100」へ訂正</t>
         </is>
       </c>
     </row>

--- a/売上レポート/売上集計_2026年6-9月.xlsx
+++ b/売上レポート/売上集計_2026年6-9月.xlsx
@@ -1074,7 +1074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1399,7 +1399,7 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>・7月は7/21〜7/24の日別報告なし。7/26は訂正後の695,890円（7月合算13,369,100）を採用。</t>
+          <t>・7月は7/24のみ日別報告なし（累計から逆算すると481,280円相当）。7/26は訂正後の695,890円（7月合算13,369,100）を採用。</t>
         </is>
       </c>
     </row>
@@ -1447,6 +1447,13 @@
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- 7/21: 前日累計10,342,730+当日329,260=10,671,990 だがLINE累計は10,763,100（差 +91,110）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">　- 7/26: 前日累計12,654,100+当日695,890=13,349,990 だがLINE累計は13,369,100（差 +19,110）</t>
         </is>
@@ -3194,100 +3201,120 @@
       <c r="H51" s="17" t="n">
         <v>10342730</v>
       </c>
-      <c r="I51" s="16" t="inlineStr"/>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>LINE上の累計10,342,730は誤記と思われる（正しくは10,433,840。翌日以降の累計はこちらに整合）</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="12" t="n">
+      <c r="A52" s="18" t="n">
         <v>46224</v>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="C52" s="13" t="n">
+      <c r="C52" s="19" t="n">
         <v>21</v>
       </c>
-      <c r="D52" s="13" t="inlineStr">
+      <c r="D52" s="19" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>平日</t>
-        </is>
-      </c>
-      <c r="F52" s="14" t="n"/>
-      <c r="G52" s="13" t="n"/>
-      <c r="H52" s="14" t="n"/>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>未報告（LINEに記載なし）</t>
+      <c r="E52" s="19" t="inlineStr">
+        <is>
+          <t>平日</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="n">
+        <v>329260</v>
+      </c>
+      <c r="G52" s="19" t="inlineStr">
+        <is>
+          <t>もたい</t>
+        </is>
+      </c>
+      <c r="H52" s="20" t="n">
+        <v>10763100</v>
+      </c>
+      <c r="I52" s="19" t="inlineStr">
+        <is>
+          <t>LINE上は「329.260」と表記（329,260円と判断）</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="12" t="n">
+      <c r="A53" s="18" t="n">
         <v>46225</v>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B53" s="19" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="C53" s="13" t="n">
+      <c r="C53" s="19" t="n">
         <v>22</v>
       </c>
-      <c r="D53" s="13" t="inlineStr">
+      <c r="D53" s="19" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="E53" s="13" t="inlineStr">
-        <is>
-          <t>平日</t>
-        </is>
-      </c>
-      <c r="F53" s="14" t="n"/>
-      <c r="G53" s="13" t="n"/>
-      <c r="H53" s="14" t="n"/>
-      <c r="I53" s="13" t="inlineStr">
-        <is>
-          <t>未報告（LINEに記載なし）</t>
-        </is>
-      </c>
+      <c r="E53" s="19" t="inlineStr">
+        <is>
+          <t>平日</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="n">
+        <v>376880</v>
+      </c>
+      <c r="G53" s="19" t="inlineStr">
+        <is>
+          <t>棚橋</t>
+        </is>
+      </c>
+      <c r="H53" s="20" t="n">
+        <v>11139980</v>
+      </c>
+      <c r="I53" s="19" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="12" t="n">
+      <c r="A54" s="18" t="n">
         <v>46226</v>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B54" s="19" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="C54" s="13" t="n">
+      <c r="C54" s="19" t="n">
         <v>23</v>
       </c>
-      <c r="D54" s="13" t="inlineStr">
+      <c r="D54" s="19" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="E54" s="13" t="inlineStr">
-        <is>
-          <t>平日</t>
-        </is>
-      </c>
-      <c r="F54" s="14" t="n"/>
-      <c r="G54" s="13" t="n"/>
-      <c r="H54" s="14" t="n"/>
-      <c r="I54" s="13" t="inlineStr">
-        <is>
-          <t>未報告（LINEに記載なし）</t>
-        </is>
-      </c>
+      <c r="E54" s="19" t="inlineStr">
+        <is>
+          <t>平日</t>
+        </is>
+      </c>
+      <c r="F54" s="20" t="n">
+        <v>417540</v>
+      </c>
+      <c r="G54" s="19" t="inlineStr">
+        <is>
+          <t>もたい</t>
+        </is>
+      </c>
+      <c r="H54" s="20" t="n">
+        <v>11557520</v>
+      </c>
+      <c r="I54" s="19" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="n">
@@ -6055,6 +6082,9 @@
       <c r="B22" s="22" t="n">
         <v>636370</v>
       </c>
+      <c r="C22" s="22" t="n">
+        <v>329260</v>
+      </c>
       <c r="E22" s="22" t="n">
         <v>606440</v>
       </c>
@@ -6066,6 +6096,9 @@
       <c r="B23" s="22" t="n">
         <v>386840</v>
       </c>
+      <c r="C23" s="22" t="n">
+        <v>376880</v>
+      </c>
       <c r="E23" s="22" t="n">
         <v>471650</v>
       </c>
@@ -6076,6 +6109,9 @@
       </c>
       <c r="B24" s="22" t="n">
         <v>377840</v>
+      </c>
+      <c r="C24" s="22" t="n">
+        <v>417540</v>
       </c>
       <c r="E24" s="22" t="n">
         <v>425490</v>

--- a/売上レポート/売上集計_2026年6-9月.xlsx
+++ b/売上レポート/売上集計_2026年6-9月.xlsx
@@ -1074,7 +1074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1399,7 +1399,7 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>・7月は7/24のみ日別報告なし（累計から逆算すると481,280円相当）。7/26は訂正後の695,890円（7月合算13,369,100）を採用。</t>
+          <t>・7月は全31日の日別報告あり。7/20・7/24の累計の誤記は翌日以降の報告（7/26訂正含む）で解消済み。7/26は訂正後の695,890円（7月合算13,369,100）を採用。</t>
         </is>
       </c>
     </row>
@@ -1454,6 +1454,13 @@
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- 7/24: 前日累計11,557,520+当日500,390=12,057,910 だがLINE累計は12,038,800（差 -19,110）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">　- 7/26: 前日累計12,654,100+当日695,890=13,349,990 だがLINE累計は13,369,100（差 +19,110）</t>
         </is>
@@ -3317,33 +3324,41 @@
       <c r="I54" s="19" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="n">
+      <c r="A55" s="18" t="n">
         <v>46227</v>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B55" s="19" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="C55" s="13" t="n">
+      <c r="C55" s="19" t="n">
         <v>24</v>
       </c>
-      <c r="D55" s="13" t="inlineStr">
+      <c r="D55" s="19" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="E55" s="13" t="inlineStr">
-        <is>
-          <t>平日</t>
-        </is>
-      </c>
-      <c r="F55" s="14" t="n"/>
-      <c r="G55" s="13" t="n"/>
-      <c r="H55" s="14" t="n"/>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>未報告（LINEに記載なし）</t>
+      <c r="E55" s="19" t="inlineStr">
+        <is>
+          <t>平日</t>
+        </is>
+      </c>
+      <c r="F55" s="20" t="n">
+        <v>500390</v>
+      </c>
+      <c r="G55" s="19" t="inlineStr">
+        <is>
+          <t>棚橋</t>
+        </is>
+      </c>
+      <c r="H55" s="20" t="n">
+        <v>12038800</v>
+      </c>
+      <c r="I55" s="19" t="inlineStr">
+        <is>
+          <t>LINE上の累計12,038,800は計算ミスと思われる（正しくは12,057,910。7/26の訂正後累計13,369,100と整合）</t>
         </is>
       </c>
     </row>
@@ -6124,6 +6139,9 @@
       <c r="B25" s="22" t="n">
         <v>428620</v>
       </c>
+      <c r="C25" s="22" t="n">
+        <v>500390</v>
+      </c>
       <c r="D25" s="22" t="n">
         <v>268730</v>
       </c>
